--- a/output/daily_report_2026-07-26.xlsx
+++ b/output/daily_report_2026-07-26.xlsx
@@ -436,7 +436,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-26 17:15:39</t>
+          <t>2026-07-26 17:42:20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
